--- a/ABA_mining/outputs/eval/task3/TASK3_VERIFY_MASTER_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/TASK3_VERIFY_MASTER_SUMMARY.xlsx
@@ -541,16 +541,16 @@
         <v>38</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.421053</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4933920704845814</v>
+        <v>0.493392</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5436507936507936</v>
+        <v>0.543651</v>
       </c>
     </row>
     <row r="3">
@@ -600,16 +600,16 @@
         <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>0.417910447761194</v>
+        <v>0.41791</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4912280701754387</v>
+        <v>0.491228</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.539683</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +659,16 @@
         <v>38</v>
       </c>
       <c r="L4" t="n">
-        <v>0.417910447761194</v>
+        <v>0.41791</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4912280701754387</v>
+        <v>0.491228</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.539683</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O5" t="n">
         <v>0.625</v>
@@ -783,7 +783,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O6" t="n">
         <v>0.625</v>
@@ -842,7 +842,7 @@
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O7" t="n">
         <v>0.625</v>
@@ -895,16 +895,16 @@
         <v>17</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8990610328638498</v>
+        <v>0.899061</v>
       </c>
       <c r="M8" t="n">
         <v>0.9575</v>
       </c>
       <c r="N8" t="n">
-        <v>0.927360774818402</v>
+        <v>0.927361</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8681318681318682</v>
+        <v>0.868132</v>
       </c>
     </row>
     <row r="9">
@@ -954,16 +954,16 @@
         <v>17</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8990610328638498</v>
+        <v>0.899061</v>
       </c>
       <c r="M9" t="n">
         <v>0.9575</v>
       </c>
       <c r="N9" t="n">
-        <v>0.927360774818402</v>
+        <v>0.927361</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8681318681318682</v>
+        <v>0.868132</v>
       </c>
     </row>
     <row r="10">
@@ -1013,16 +1013,16 @@
         <v>17</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8990610328638498</v>
+        <v>0.899061</v>
       </c>
       <c r="M10" t="n">
         <v>0.9575</v>
       </c>
       <c r="N10" t="n">
-        <v>0.927360774818402</v>
+        <v>0.927361</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8681318681318682</v>
+        <v>0.868132</v>
       </c>
     </row>
     <row r="11">
@@ -1072,13 +1072,13 @@
         <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3924914675767918</v>
+        <v>0.392491</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5156950672645739</v>
+        <v>0.515695</v>
       </c>
       <c r="O11" t="n">
         <v>0.5679999999999999</v>
@@ -1131,13 +1131,13 @@
         <v>38</v>
       </c>
       <c r="L12" t="n">
-        <v>0.391156462585034</v>
+        <v>0.391156</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5145413870246085</v>
+        <v>0.514541</v>
       </c>
       <c r="O12" t="n">
         <v>0.5659999999999999</v>
@@ -1190,13 +1190,13 @@
         <v>38</v>
       </c>
       <c r="L13" t="n">
-        <v>0.391156462585034</v>
+        <v>0.391156</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5145413870246085</v>
+        <v>0.514541</v>
       </c>
       <c r="O13" t="n">
         <v>0.5659999999999999</v>
@@ -1252,13 +1252,13 @@
         <v>0.375</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.861702</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
     </row>
     <row r="15">
@@ -1311,13 +1311,13 @@
         <v>0.375</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.861702</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
     </row>
     <row r="16">
@@ -1370,13 +1370,13 @@
         <v>0.375</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8617021276595744</v>
+        <v>0.861702</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
     </row>
     <row r="17">
@@ -1432,7 +1432,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O17" t="n">
         <v>0.625</v>
@@ -1491,7 +1491,7 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O18" t="n">
         <v>0.625</v>
@@ -1550,7 +1550,7 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O19" t="n">
         <v>0.625</v>
@@ -1603,16 +1603,16 @@
         <v>9</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8967889908256881</v>
+        <v>0.8967889999999999</v>
       </c>
       <c r="M20" t="n">
         <v>0.9775</v>
       </c>
       <c r="N20" t="n">
-        <v>0.9354066985645932</v>
+        <v>0.935407</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8813186813186813</v>
+        <v>0.881319</v>
       </c>
     </row>
     <row r="21">
@@ -1662,16 +1662,16 @@
         <v>9</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8967889908256881</v>
+        <v>0.8967889999999999</v>
       </c>
       <c r="M21" t="n">
         <v>0.9775</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9354066985645932</v>
+        <v>0.935407</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8813186813186813</v>
+        <v>0.881319</v>
       </c>
     </row>
     <row r="22">
@@ -1721,16 +1721,16 @@
         <v>9</v>
       </c>
       <c r="L22" t="n">
-        <v>0.8967889908256881</v>
+        <v>0.8967889999999999</v>
       </c>
       <c r="M22" t="n">
         <v>0.9775</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9354066985645932</v>
+        <v>0.935407</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8813186813186813</v>
+        <v>0.881319</v>
       </c>
     </row>
     <row r="23">
@@ -1780,13 +1780,13 @@
         <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3202614379084967</v>
+        <v>0.320261</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.960784</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4803921568627452</v>
+        <v>0.480392</v>
       </c>
       <c r="O23" t="n">
         <v>0.364</v>
@@ -1839,13 +1839,13 @@
         <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3202614379084967</v>
+        <v>0.320261</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.960784</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4803921568627452</v>
+        <v>0.480392</v>
       </c>
       <c r="O24" t="n">
         <v>0.364</v>
@@ -1898,13 +1898,13 @@
         <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>0.3202614379084967</v>
+        <v>0.320261</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.960784</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4803921568627452</v>
+        <v>0.480392</v>
       </c>
       <c r="O25" t="n">
         <v>0.364</v>
@@ -1957,16 +1957,16 @@
         <v>65</v>
       </c>
       <c r="L26" t="n">
-        <v>0.3815789473684211</v>
+        <v>0.381579</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3085106382978723</v>
+        <v>0.308511</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3411764705882353</v>
+        <v>0.341177</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.555556</v>
       </c>
     </row>
     <row r="27">
@@ -2016,16 +2016,16 @@
         <v>65</v>
       </c>
       <c r="L27" t="n">
-        <v>0.3815789473684211</v>
+        <v>0.381579</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3085106382978723</v>
+        <v>0.308511</v>
       </c>
       <c r="N27" t="n">
-        <v>0.3411764705882353</v>
+        <v>0.341177</v>
       </c>
       <c r="O27" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.555556</v>
       </c>
     </row>
     <row r="28">
@@ -2075,16 +2075,16 @@
         <v>65</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3815789473684211</v>
+        <v>0.381579</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3085106382978723</v>
+        <v>0.308511</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3411764705882353</v>
+        <v>0.341177</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.555556</v>
       </c>
     </row>
     <row r="29">
@@ -2311,16 +2311,16 @@
         <v>126</v>
       </c>
       <c r="L32" t="n">
-        <v>0.898360655737705</v>
+        <v>0.898361</v>
       </c>
       <c r="M32" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>0.7773049645390072</v>
+        <v>0.777305</v>
       </c>
       <c r="O32" t="n">
-        <v>0.6549450549450549</v>
+        <v>0.654945</v>
       </c>
     </row>
     <row r="33">
@@ -2370,16 +2370,16 @@
         <v>126</v>
       </c>
       <c r="L33" t="n">
-        <v>0.898360655737705</v>
+        <v>0.898361</v>
       </c>
       <c r="M33" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>0.7773049645390072</v>
+        <v>0.777305</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6549450549450549</v>
+        <v>0.654945</v>
       </c>
     </row>
     <row r="34">
@@ -2429,16 +2429,16 @@
         <v>126</v>
       </c>
       <c r="L34" t="n">
-        <v>0.898360655737705</v>
+        <v>0.898361</v>
       </c>
       <c r="M34" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>0.7773049645390072</v>
+        <v>0.777305</v>
       </c>
       <c r="O34" t="n">
-        <v>0.6549450549450549</v>
+        <v>0.654945</v>
       </c>
     </row>
     <row r="35">
@@ -2488,13 +2488,13 @@
         <v>60</v>
       </c>
       <c r="L35" t="n">
-        <v>0.3321428571428571</v>
+        <v>0.332143</v>
       </c>
       <c r="M35" t="n">
-        <v>0.6078431372549019</v>
+        <v>0.607843</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4295612009237875</v>
+        <v>0.429561</v>
       </c>
       <c r="O35" t="n">
         <v>0.506</v>
@@ -2547,13 +2547,13 @@
         <v>60</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3321428571428571</v>
+        <v>0.332143</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6078431372549019</v>
+        <v>0.607843</v>
       </c>
       <c r="N36" t="n">
-        <v>0.4295612009237875</v>
+        <v>0.429561</v>
       </c>
       <c r="O36" t="n">
         <v>0.506</v>
@@ -2606,13 +2606,13 @@
         <v>60</v>
       </c>
       <c r="L37" t="n">
-        <v>0.3321428571428571</v>
+        <v>0.332143</v>
       </c>
       <c r="M37" t="n">
-        <v>0.6078431372549019</v>
+        <v>0.607843</v>
       </c>
       <c r="N37" t="n">
-        <v>0.4295612009237875</v>
+        <v>0.429561</v>
       </c>
       <c r="O37" t="n">
         <v>0.506</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.626984126984127</v>
+        <v>0.626984</v>
       </c>
     </row>
     <row r="39">
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0.626984126984127</v>
+        <v>0.626984</v>
       </c>
     </row>
     <row r="40">
@@ -2792,7 +2792,7 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0.626984126984127</v>
+        <v>0.626984</v>
       </c>
     </row>
     <row r="41">
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0.1208791208791209</v>
+        <v>0.120879</v>
       </c>
     </row>
     <row r="45">
@@ -3087,7 +3087,7 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0.1208791208791209</v>
+        <v>0.120879</v>
       </c>
     </row>
     <row r="46">
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0.1208791208791209</v>
+        <v>0.120879</v>
       </c>
     </row>
     <row r="47">
@@ -3373,16 +3373,16 @@
         <v>11</v>
       </c>
       <c r="L50" t="n">
-        <v>0.4048780487804878</v>
+        <v>0.404878</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8829787234042553</v>
+        <v>0.882979</v>
       </c>
       <c r="N50" t="n">
-        <v>0.5551839464882943</v>
+        <v>0.555184</v>
       </c>
       <c r="O50" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.472222</v>
       </c>
     </row>
     <row r="51">
@@ -3432,16 +3432,16 @@
         <v>11</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4048780487804878</v>
+        <v>0.404878</v>
       </c>
       <c r="M51" t="n">
-        <v>0.8829787234042553</v>
+        <v>0.882979</v>
       </c>
       <c r="N51" t="n">
-        <v>0.5551839464882943</v>
+        <v>0.555184</v>
       </c>
       <c r="O51" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.472222</v>
       </c>
     </row>
     <row r="52">
@@ -3491,16 +3491,16 @@
         <v>11</v>
       </c>
       <c r="L52" t="n">
-        <v>0.4048780487804878</v>
+        <v>0.404878</v>
       </c>
       <c r="M52" t="n">
-        <v>0.8829787234042553</v>
+        <v>0.882979</v>
       </c>
       <c r="N52" t="n">
-        <v>0.5551839464882943</v>
+        <v>0.555184</v>
       </c>
       <c r="O52" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.472222</v>
       </c>
     </row>
     <row r="53">
@@ -3550,13 +3550,13 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.714286</v>
       </c>
       <c r="M53" t="n">
         <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.833334</v>
       </c>
       <c r="O53" t="n">
         <v>0.75</v>
@@ -3609,13 +3609,13 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.714286</v>
       </c>
       <c r="M54" t="n">
         <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.833334</v>
       </c>
       <c r="O54" t="n">
         <v>0.75</v>
@@ -3668,13 +3668,13 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.714286</v>
       </c>
       <c r="M55" t="n">
         <v>1</v>
       </c>
       <c r="N55" t="n">
-        <v>0.8333333333333333</v>
+        <v>0.833334</v>
       </c>
       <c r="O55" t="n">
         <v>0.75</v>
@@ -3727,16 +3727,16 @@
         <v>27</v>
       </c>
       <c r="L56" t="n">
-        <v>0.9232673267326733</v>
+        <v>0.9232669999999999</v>
       </c>
       <c r="M56" t="n">
         <v>0.9325</v>
       </c>
       <c r="N56" t="n">
-        <v>0.927860696517413</v>
+        <v>0.927861</v>
       </c>
       <c r="O56" t="n">
-        <v>0.8725274725274725</v>
+        <v>0.8725270000000001</v>
       </c>
     </row>
     <row r="57">
@@ -3786,16 +3786,16 @@
         <v>28</v>
       </c>
       <c r="L57" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.923077</v>
       </c>
       <c r="M57" t="n">
         <v>0.93</v>
       </c>
       <c r="N57" t="n">
-        <v>0.9265255292652554</v>
+        <v>0.926526</v>
       </c>
       <c r="O57" t="n">
-        <v>0.8703296703296703</v>
+        <v>0.87033</v>
       </c>
     </row>
     <row r="58">
@@ -3845,16 +3845,16 @@
         <v>28</v>
       </c>
       <c r="L58" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.923077</v>
       </c>
       <c r="M58" t="n">
         <v>0.93</v>
       </c>
       <c r="N58" t="n">
-        <v>0.9265255292652554</v>
+        <v>0.926526</v>
       </c>
       <c r="O58" t="n">
-        <v>0.8703296703296703</v>
+        <v>0.87033</v>
       </c>
     </row>
     <row r="59">
@@ -3904,13 +3904,13 @@
         <v>38</v>
       </c>
       <c r="L59" t="n">
-        <v>0.3257790368271954</v>
+        <v>0.325779</v>
       </c>
       <c r="M59" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="N59" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.454545</v>
       </c>
       <c r="O59" t="n">
         <v>0.448</v>
@@ -3963,13 +3963,13 @@
         <v>38</v>
       </c>
       <c r="L60" t="n">
-        <v>0.3257790368271954</v>
+        <v>0.325779</v>
       </c>
       <c r="M60" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="N60" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.454545</v>
       </c>
       <c r="O60" t="n">
         <v>0.448</v>
@@ -4022,13 +4022,13 @@
         <v>38</v>
       </c>
       <c r="L61" t="n">
-        <v>0.3257790368271954</v>
+        <v>0.325779</v>
       </c>
       <c r="M61" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="N61" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.454545</v>
       </c>
       <c r="O61" t="n">
         <v>0.448</v>
@@ -4081,16 +4081,16 @@
         <v>58</v>
       </c>
       <c r="L62" t="n">
-        <v>0.4235294117647059</v>
+        <v>0.423529</v>
       </c>
       <c r="M62" t="n">
-        <v>0.3829787234042553</v>
+        <v>0.382979</v>
       </c>
       <c r="N62" t="n">
-        <v>0.4022346368715084</v>
+        <v>0.402235</v>
       </c>
       <c r="O62" t="n">
-        <v>0.5753968253968254</v>
+        <v>0.575397</v>
       </c>
     </row>
     <row r="63">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>check-out</t>
+          <t>check-in</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4125,31 +4125,31 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>8</v>
+        <v>252</v>
       </c>
       <c r="H63" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L63" t="n">
-        <v>0.625</v>
+        <v>0.419753</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0.361702</v>
       </c>
       <c r="N63" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.388571</v>
       </c>
       <c r="O63" t="n">
-        <v>0.625</v>
+        <v>0.575397</v>
       </c>
     </row>
     <row r="64">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>check-out</t>
+          <t>check-in</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4184,31 +4184,31 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>8</v>
+        <v>252</v>
       </c>
       <c r="H64" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J64" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L64" t="n">
-        <v>0.625</v>
+        <v>0.419753</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0.361702</v>
       </c>
       <c r="N64" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.388571</v>
       </c>
       <c r="O64" t="n">
-        <v>0.625</v>
+        <v>0.575397</v>
       </c>
     </row>
     <row r="65">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Test 1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4264,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O65" t="n">
         <v>0.625</v>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>check-out</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4302,31 +4302,31 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>455</v>
+        <v>8</v>
       </c>
       <c r="H66" t="n">
-        <v>303</v>
+        <v>5</v>
       </c>
       <c r="I66" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K66" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.8964497041420119</v>
+        <v>0.625</v>
       </c>
       <c r="M66" t="n">
-        <v>0.7575</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>0.8211382113821138</v>
+        <v>0.769231</v>
       </c>
       <c r="O66" t="n">
-        <v>0.7098901098901099</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="67">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>check-out</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4361,31 +4361,31 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>455</v>
+        <v>8</v>
       </c>
       <c r="H67" t="n">
-        <v>302</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="K67" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0.8961424332344213</v>
+        <v>0.625</v>
       </c>
       <c r="M67" t="n">
-        <v>0.755</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
-        <v>0.819538670284939</v>
+        <v>0.769231</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7076923076923077</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="68">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Test 1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4435,16 +4435,16 @@
         <v>97</v>
       </c>
       <c r="L68" t="n">
-        <v>0.8964497041420119</v>
+        <v>0.89645</v>
       </c>
       <c r="M68" t="n">
         <v>0.7575</v>
       </c>
       <c r="N68" t="n">
-        <v>0.8211382113821138</v>
+        <v>0.821138</v>
       </c>
       <c r="O68" t="n">
-        <v>0.7098901098901099</v>
+        <v>0.70989</v>
       </c>
     </row>
     <row r="69">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4479,31 +4479,31 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>500</v>
+        <v>455</v>
       </c>
       <c r="H69" t="n">
-        <v>88</v>
+        <v>302</v>
       </c>
       <c r="I69" t="n">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="K69" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="L69" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.896142</v>
       </c>
       <c r="M69" t="n">
-        <v>0.5751633986928104</v>
+        <v>0.755</v>
       </c>
       <c r="N69" t="n">
-        <v>0.4929971988795518</v>
+        <v>0.819538</v>
       </c>
       <c r="O69" t="n">
-        <v>0.638</v>
+        <v>0.707692</v>
       </c>
     </row>
     <row r="70">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4538,31 +4538,31 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>500</v>
+        <v>455</v>
       </c>
       <c r="H70" t="n">
-        <v>88</v>
+        <v>303</v>
       </c>
       <c r="I70" t="n">
-        <v>231</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="K70" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="L70" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.89645</v>
       </c>
       <c r="M70" t="n">
-        <v>0.5751633986928104</v>
+        <v>0.7575</v>
       </c>
       <c r="N70" t="n">
-        <v>0.4929971988795518</v>
+        <v>0.821138</v>
       </c>
       <c r="O70" t="n">
-        <v>0.638</v>
+        <v>0.70989</v>
       </c>
     </row>
     <row r="71">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Test 1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4612,13 +4612,13 @@
         <v>65</v>
       </c>
       <c r="L71" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.431373</v>
       </c>
       <c r="M71" t="n">
-        <v>0.5751633986928104</v>
+        <v>0.575163</v>
       </c>
       <c r="N71" t="n">
-        <v>0.4929971988795518</v>
+        <v>0.492997</v>
       </c>
       <c r="O71" t="n">
         <v>0.638</v>
@@ -4632,12 +4632,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>one_shot</t>
+          <t>contrary_v6</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>check-in</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4656,31 +4656,31 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>252</v>
+        <v>500</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="I72" t="n">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="K72" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>0.431373</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>0.575163</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>0.492997</v>
       </c>
       <c r="O72" t="n">
-        <v>0.623015873015873</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="73">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>one_shot</t>
+          <t>contrary_v6</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>check-in</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4715,31 +4715,31 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>252</v>
+        <v>500</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="I73" t="n">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="K73" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>0.431373</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>0.575163</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>0.492997</v>
       </c>
       <c r="O73" t="n">
-        <v>0.623015873015873</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="74">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Test 1</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4798,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>0.623015873015873</v>
+        <v>0.623016</v>
       </c>
     </row>
     <row r="75">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>check-out</t>
+          <t>check-in</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4833,31 +4833,31 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>8</v>
+        <v>252</v>
       </c>
       <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>157</v>
+      </c>
+      <c r="J75" t="n">
         <v>1</v>
       </c>
-      <c r="I75" t="n">
-        <v>3</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
       <c r="K75" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0.3333333333333334</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>0.5</v>
+        <v>0.623016</v>
       </c>
     </row>
     <row r="76">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>check-out</t>
+          <t>check-in</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4892,31 +4892,31 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>8</v>
+        <v>252</v>
       </c>
       <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>157</v>
+      </c>
+      <c r="J76" t="n">
         <v>1</v>
       </c>
-      <c r="I76" t="n">
-        <v>3</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
       <c r="K76" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0.3333333333333334</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>0.5</v>
+        <v>0.623016</v>
       </c>
     </row>
     <row r="77">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Test 1</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4972,7 +4972,7 @@
         <v>0.2</v>
       </c>
       <c r="N77" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.333333</v>
       </c>
       <c r="O77" t="n">
         <v>0.5</v>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>check-out</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5010,31 +5010,31 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>455</v>
+        <v>8</v>
       </c>
       <c r="H78" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>302</v>
+        <v>4</v>
       </c>
       <c r="L78" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>0.245</v>
+        <v>0.2</v>
       </c>
       <c r="N78" t="n">
-        <v>0.392</v>
+        <v>0.333333</v>
       </c>
       <c r="O78" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="79">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>check-out</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5069,31 +5069,31 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>455</v>
+        <v>8</v>
       </c>
       <c r="H79" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="I79" t="n">
-        <v>53</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>302</v>
+        <v>4</v>
       </c>
       <c r="L79" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>0.245</v>
+        <v>0.2</v>
       </c>
       <c r="N79" t="n">
-        <v>0.392</v>
+        <v>0.333333</v>
       </c>
       <c r="O79" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="80">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Test 1</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5152,7 +5152,7 @@
         <v>0.392</v>
       </c>
       <c r="O80" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.331868</v>
       </c>
     </row>
     <row r="81">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -5187,31 +5187,31 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>500</v>
+        <v>455</v>
       </c>
       <c r="H81" t="n">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="I81" t="n">
-        <v>322</v>
+        <v>53</v>
       </c>
       <c r="J81" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K81" t="n">
-        <v>131</v>
+        <v>302</v>
       </c>
       <c r="L81" t="n">
-        <v>0.4680851063829787</v>
+        <v>0.98</v>
       </c>
       <c r="M81" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.245</v>
       </c>
       <c r="N81" t="n">
-        <v>0.22</v>
+        <v>0.392</v>
       </c>
       <c r="O81" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.331868</v>
       </c>
     </row>
     <row r="82">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>staff</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -5246,31 +5246,31 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>500</v>
+        <v>455</v>
       </c>
       <c r="H82" t="n">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="I82" t="n">
-        <v>321</v>
+        <v>53</v>
       </c>
       <c r="J82" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K82" t="n">
-        <v>131</v>
+        <v>302</v>
       </c>
       <c r="L82" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.98</v>
       </c>
       <c r="M82" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.245</v>
       </c>
       <c r="N82" t="n">
-        <v>0.2189054726368159</v>
+        <v>0.392</v>
       </c>
       <c r="O82" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.331868</v>
       </c>
     </row>
     <row r="83">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Test 1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -5311,25 +5311,25 @@
         <v>22</v>
       </c>
       <c r="I83" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J83" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K83" t="n">
         <v>131</v>
       </c>
       <c r="L83" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.468085</v>
       </c>
       <c r="M83" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.143791</v>
       </c>
       <c r="N83" t="n">
-        <v>0.2189054726368159</v>
+        <v>0.22</v>
       </c>
       <c r="O83" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>zero_shot</t>
+          <t>one_shot</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>check-in</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -5364,31 +5364,31 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>252</v>
+        <v>500</v>
       </c>
       <c r="H84" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="I84" t="n">
-        <v>71</v>
+        <v>321</v>
       </c>
       <c r="J84" t="n">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="K84" t="n">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="L84" t="n">
-        <v>0.4</v>
+        <v>0.458333</v>
       </c>
       <c r="M84" t="n">
-        <v>0.6170212765957447</v>
+        <v>0.143791</v>
       </c>
       <c r="N84" t="n">
-        <v>0.4853556485355649</v>
+        <v>0.218906</v>
       </c>
       <c r="O84" t="n">
-        <v>0.5119047619047619</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="85">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>zero_shot</t>
+          <t>one_shot</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>check-in</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -5423,31 +5423,31 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>252</v>
+        <v>500</v>
       </c>
       <c r="H85" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="I85" t="n">
-        <v>70</v>
+        <v>321</v>
       </c>
       <c r="J85" t="n">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="K85" t="n">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="L85" t="n">
-        <v>0.3931034482758621</v>
+        <v>0.458333</v>
       </c>
       <c r="M85" t="n">
-        <v>0.6063829787234043</v>
+        <v>0.143791</v>
       </c>
       <c r="N85" t="n">
-        <v>0.4769874476987448</v>
+        <v>0.218906</v>
       </c>
       <c r="O85" t="n">
-        <v>0.503968253968254</v>
+        <v>0.6860000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Test 1</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5488,25 +5488,25 @@
         <v>58</v>
       </c>
       <c r="I86" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J86" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K86" t="n">
         <v>36</v>
       </c>
       <c r="L86" t="n">
-        <v>0.3972602739726027</v>
+        <v>0.4</v>
       </c>
       <c r="M86" t="n">
-        <v>0.6170212765957447</v>
+        <v>0.617021</v>
       </c>
       <c r="N86" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.485356</v>
       </c>
       <c r="O86" t="n">
-        <v>0.5079365079365079</v>
+        <v>0.5119050000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>check-out</t>
+          <t>check-in</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5541,31 +5541,31 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>8</v>
+        <v>252</v>
       </c>
       <c r="H87" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J87" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L87" t="n">
-        <v>0.625</v>
+        <v>0.393103</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0.606383</v>
       </c>
       <c r="N87" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.476987</v>
       </c>
       <c r="O87" t="n">
-        <v>0.625</v>
+        <v>0.503968</v>
       </c>
     </row>
     <row r="88">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>check-out</t>
+          <t>check-in</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Test 2</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5600,31 +5600,31 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>8</v>
+        <v>252</v>
       </c>
       <c r="H88" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J88" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="L88" t="n">
-        <v>0.625</v>
+        <v>0.39726</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0.617021</v>
       </c>
       <c r="N88" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.483333</v>
       </c>
       <c r="O88" t="n">
-        <v>0.625</v>
+        <v>0.507937</v>
       </c>
     </row>
     <row r="89">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Test 3</t>
+          <t>Test 1</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5680,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="O89" t="n">
         <v>0.625</v>
@@ -5699,50 +5699,50 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>check-out</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Contrary(N)Body(N)</t>
+          <t>Contrary(P)Body(N)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 2</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G90" t="n">
+        <v>8</v>
+      </c>
+      <c r="H90" t="n">
         <v>5</v>
       </c>
-      <c r="H90" t="n">
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>3</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="M90" t="n">
         <v>1</v>
       </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>4</v>
-      </c>
-      <c r="L90" t="n">
-        <v>1</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0.2</v>
-      </c>
       <c r="N90" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.769231</v>
       </c>
       <c r="O90" t="n">
-        <v>0.2</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="91">
@@ -5758,50 +5758,50 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>check-out</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Contrary(P)Body(P)</t>
+          <t>Contrary(P)Body(N)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Test 1</t>
+          <t>Test 3</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G91" t="n">
+        <v>8</v>
+      </c>
+      <c r="H91" t="n">
         <v>5</v>
       </c>
-      <c r="H91" t="n">
-        <v>2</v>
-      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="M91" t="n">
         <v>1</v>
       </c>
-      <c r="M91" t="n">
-        <v>0.4</v>
-      </c>
       <c r="N91" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.769231</v>
       </c>
       <c r="O91" t="n">
-        <v>0.4</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="92">
@@ -5851,16 +5851,16 @@
         <v>44</v>
       </c>
       <c r="L92" t="n">
-        <v>0.8944723618090452</v>
+        <v>0.894472</v>
       </c>
       <c r="M92" t="n">
         <v>0.89</v>
       </c>
       <c r="N92" t="n">
-        <v>0.8922305764411028</v>
+        <v>0.89223</v>
       </c>
       <c r="O92" t="n">
-        <v>0.810989010989011</v>
+        <v>0.810989</v>
       </c>
     </row>
     <row r="93">
@@ -5910,16 +5910,16 @@
         <v>44</v>
       </c>
       <c r="L93" t="n">
-        <v>0.8944723618090452</v>
+        <v>0.894472</v>
       </c>
       <c r="M93" t="n">
         <v>0.89</v>
       </c>
       <c r="N93" t="n">
-        <v>0.8922305764411028</v>
+        <v>0.89223</v>
       </c>
       <c r="O93" t="n">
-        <v>0.810989010989011</v>
+        <v>0.810989</v>
       </c>
     </row>
     <row r="94">
@@ -5969,16 +5969,16 @@
         <v>45</v>
       </c>
       <c r="L94" t="n">
-        <v>0.8942065491183879</v>
+        <v>0.894207</v>
       </c>
       <c r="M94" t="n">
         <v>0.8875</v>
       </c>
       <c r="N94" t="n">
-        <v>0.890840652446675</v>
+        <v>0.890841</v>
       </c>
       <c r="O94" t="n">
-        <v>0.8087912087912088</v>
+        <v>0.808791</v>
       </c>
     </row>
     <row r="95">
@@ -6028,13 +6028,13 @@
         <v>29</v>
       </c>
       <c r="L95" t="n">
-        <v>0.3768996960486322</v>
+        <v>0.3769</v>
       </c>
       <c r="M95" t="n">
-        <v>0.8104575163398693</v>
+        <v>0.810458</v>
       </c>
       <c r="N95" t="n">
-        <v>0.5145228215767635</v>
+        <v>0.514523</v>
       </c>
       <c r="O95" t="n">
         <v>0.532</v>
@@ -6087,13 +6087,13 @@
         <v>29</v>
       </c>
       <c r="L96" t="n">
-        <v>0.3723723723723724</v>
+        <v>0.372372</v>
       </c>
       <c r="M96" t="n">
-        <v>0.8104575163398693</v>
+        <v>0.810458</v>
       </c>
       <c r="N96" t="n">
-        <v>0.5102880658436214</v>
+        <v>0.510288</v>
       </c>
       <c r="O96" t="n">
         <v>0.524</v>
@@ -6146,13 +6146,13 @@
         <v>30</v>
       </c>
       <c r="L97" t="n">
-        <v>0.3716012084592145</v>
+        <v>0.371601</v>
       </c>
       <c r="M97" t="n">
-        <v>0.803921568627451</v>
+        <v>0.803922</v>
       </c>
       <c r="N97" t="n">
-        <v>0.5082644628099173</v>
+        <v>0.508264</v>
       </c>
       <c r="O97" t="n">
         <v>0.524</v>
@@ -6169,7 +6169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6220,42 +6220,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Best Test (contrary_v1)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Best Test (contrary_v2)</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Best Test (contrary_v3)</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Best Test (contrary_v4)</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Best Test (contrary_v5)</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Best Test (contrary_v6)</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Best Test (one_shot)</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Best Test (zero_shot)</t>
+          <t>Best Test</t>
         </is>
       </c>
     </row>
@@ -6286,53 +6251,18 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.4189578423671118</v>
+        <v>0.418958</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.595745</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4919494036118197</v>
+        <v>0.491949</v>
       </c>
       <c r="I2" t="n">
-        <v>0.541005291005291</v>
+        <v>0.541006</v>
       </c>
       <c r="J2" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -6371,7 +6301,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="I3" t="n">
         <v>0.625</v>
@@ -6381,41 +6311,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6444,53 +6339,18 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.8990610328638496</v>
+        <v>0.899061</v>
       </c>
       <c r="G4" t="n">
         <v>0.9575</v>
       </c>
       <c r="H4" t="n">
-        <v>0.927360774818402</v>
+        <v>0.927361</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8681318681318682</v>
+        <v>0.868132</v>
       </c>
       <c r="J4" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -6523,53 +6383,18 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.3916014642489533</v>
+        <v>0.391601</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5149259471045969</v>
+        <v>0.514926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5666666666666665</v>
+        <v>0.566667</v>
       </c>
       <c r="J5" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -6605,50 +6430,15 @@
         <v>0.375</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8617021276595743</v>
+        <v>0.861702</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.522581</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4126984126984127</v>
+        <v>0.412698</v>
       </c>
       <c r="J6" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -6687,7 +6477,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="I7" t="n">
         <v>0.625</v>
@@ -6697,41 +6487,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6760,53 +6515,18 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.8967889908256881</v>
+        <v>0.8967889999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0.9775</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9354066985645932</v>
+        <v>0.935407</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8813186813186813</v>
+        <v>0.881319</v>
       </c>
       <c r="J8" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -6839,13 +6559,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.3202614379084967</v>
+        <v>0.320261</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9607843137254902</v>
+        <v>0.960784</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4803921568627452</v>
+        <v>0.480392</v>
       </c>
       <c r="I9" t="n">
         <v>0.364</v>
@@ -6855,41 +6575,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6918,53 +6603,18 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.3815789473684211</v>
+        <v>0.381579</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3085106382978723</v>
+        <v>0.308511</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3411764705882352</v>
+        <v>0.341177</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.555556</v>
       </c>
       <c r="J10" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -7013,41 +6663,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -7076,53 +6691,18 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.898360655737705</v>
+        <v>0.898361</v>
       </c>
       <c r="G12" t="n">
         <v>0.6850000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7773049645390072</v>
+        <v>0.777305</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6549450549450549</v>
+        <v>0.654945</v>
       </c>
       <c r="J12" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -7155,13 +6735,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.3321428571428571</v>
+        <v>0.332143</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6078431372549019</v>
+        <v>0.607843</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4295612009237875</v>
+        <v>0.429561</v>
       </c>
       <c r="I13" t="n">
         <v>0.506</v>
@@ -7171,41 +6751,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -7243,44 +6788,9 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0.626984126984127</v>
+        <v>0.626984</v>
       </c>
       <c r="J14" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -7329,41 +6839,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7401,44 +6876,9 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1208791208791209</v>
+        <v>0.120879</v>
       </c>
       <c r="J16" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -7487,41 +6927,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7550,53 +6955,18 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.4048780487804879</v>
+        <v>0.404878</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8829787234042553</v>
+        <v>0.882979</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5551839464882943</v>
+        <v>0.555184</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.472222</v>
       </c>
       <c r="J18" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -7629,13 +6999,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.714286</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.833334</v>
       </c>
       <c r="I19" t="n">
         <v>0.75</v>
@@ -7645,41 +7015,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7708,53 +7043,18 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.9231403909621733</v>
+        <v>0.92314</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9308333333333333</v>
+        <v>0.930833</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9269705850159746</v>
+        <v>0.926971</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8710622710622711</v>
+        <v>0.871062</v>
       </c>
       <c r="J20" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -7787,13 +7087,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.3257790368271954</v>
+        <v>0.325779</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7516339869281046</v>
+        <v>0.751634</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.454545</v>
       </c>
       <c r="I21" t="n">
         <v>0.448</v>
@@ -7803,41 +7103,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7866,53 +7131,18 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.4235294117647059</v>
+        <v>0.421012</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3829787234042553</v>
+        <v>0.368794</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4022346368715084</v>
+        <v>0.393126</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5753968253968254</v>
+        <v>0.575397</v>
       </c>
       <c r="J22" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -7951,7 +7181,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="I23" t="n">
         <v>0.625</v>
@@ -7961,41 +7191,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -8024,53 +7219,18 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.8963472805061484</v>
+        <v>0.896347</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7566666666666667</v>
+        <v>0.756667</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8206050310163889</v>
+        <v>0.820605</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7091575091575092</v>
+        <v>0.709157</v>
       </c>
       <c r="J24" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -8103,13 +7263,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.431373</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5751633986928104</v>
+        <v>0.575163</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4929971988795518</v>
+        <v>0.492997</v>
       </c>
       <c r="I25" t="n">
         <v>0.638</v>
@@ -8119,41 +7279,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8191,44 +7316,9 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0.623015873015873</v>
+        <v>0.623016</v>
       </c>
       <c r="J26" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -8267,7 +7357,7 @@
         <v>0.2</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.333333</v>
       </c>
       <c r="I27" t="n">
         <v>0.5</v>
@@ -8277,41 +7367,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8349,44 +7404,9 @@
         <v>0.392</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.331868</v>
       </c>
       <c r="J28" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -8419,53 +7439,18 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.4615839243498818</v>
+        <v>0.461584</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1437908496732026</v>
+        <v>0.143791</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2192703150912106</v>
+        <v>0.219271</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.686667</v>
       </c>
       <c r="J29" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -8498,53 +7483,18 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.3967879074161549</v>
+        <v>0.396788</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6134751773049646</v>
+        <v>0.613475</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4818921431892143</v>
+        <v>0.481892</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5079365079365079</v>
+        <v>0.507937</v>
       </c>
       <c r="J30" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -8583,7 +7533,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.769231</v>
       </c>
       <c r="I31" t="n">
         <v>0.625</v>
@@ -8593,41 +7543,6 @@
           <t>Test 1</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8642,39 +7557,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>price</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Contrary(N)Body(N)</t>
+          <t>Contrary(P)Body(N)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.894384</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>0.889167</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.891767</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+        <v>0.810256</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
@@ -8693,197 +7601,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Contrary(P)Body(P)</t>
+          <t>Contrary(P)Body(N)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0.373624</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4</v>
+        <v>0.808279</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.511025</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>llama3.2</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>zero_shot</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Contrary(P)Body(N)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0.8943837575788262</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.8891666666666667</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.8917672684429602</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.8102564102564104</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>llama3.2</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>zero_shot</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>staff</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Contrary(P)Body(N)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>0.3736244256267398</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.8082788671023966</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.5110251167434341</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.5266666666666667</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Test 1</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
+        <v>0.526667</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>Test 1</t>
         </is>
